--- a/data/trans_dic/IP19C06-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías</t>
+          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,01</t>
+          <t>0,0; 5,44</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,99</t>
+          <t>0,0; 6,12</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,24</t>
+          <t>0,0; 3,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,04</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,68</t>
+          <t>0,0; 2,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 0,95</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,64</t>
+          <t>0,0; 2,77</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,39</t>
+          <t>0,0; 2,68</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,93</t>
+          <t>0,0; 2,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 2,86</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 4,16</t>
+          <t>0,34; 4,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,12</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 1,21</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,93</t>
+          <t>0,0; 4,76</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,29</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,59</t>
+          <t>0,0; 1,56</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,72</t>
+          <t>0,37; 3,02</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,65</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,96</t>
+          <t>0,0; 5,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,6</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,84</t>
+          <t>0,0; 2,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1,56</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,78</t>
+          <t>0,0; 6,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,67</t>
+          <t>0,0; 5,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,6</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,71</t>
+          <t>0,28; 3,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,61</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,64</t>
+          <t>0,0; 5,94</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,74; 6,77</t>
+          <t>0,71; 6,56</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,15</t>
+          <t>0,0; 3,14</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,78</t>
+          <t>0,0; 4,45</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 1,38</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,7</t>
+          <t>0,4; 3,57</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 0,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,25</t>
+          <t>0,37; 3,21</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 0,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,0</t>
+          <t>0,32; 2,07</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,28</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 2,66</t>
+          <t>0,68; 2,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,2</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,78</t>
+          <t>0,01; 1,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 0,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,62</t>
+          <t>0,0; 0,73</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,38</t>
+          <t>0,35; 1,44</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,76</t>
+          <t>0,08; 0,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,44; 1,59</t>
+          <t>0,49; 1,76</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por tratamiento de las enfermedades de las encías (tasa de respuesta: 99,46%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>771</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>745</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3855</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2931</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3247</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4056</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 4156</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1730</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>582</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>617</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>3062</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2612</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3061</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>391; 4829</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>0; 7969</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3851</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3368</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>1039; 8485</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1128</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>422</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>1045</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1467</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4093</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2327</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5003</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3917</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4616</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>427; 5415</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4215</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6578</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1519</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2861</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>2885</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>2862</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 5522</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>723; 6641</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2829</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4288</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3698</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>749; 6752</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>784; 6820</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>3230</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>1388</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5758</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2377</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>5452</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>2088</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>8135</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1127; 7336</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0; 4644</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2657; 10494</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3836</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>18; 6120</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>0; 3520</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 8558</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5225</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>2505; 10386</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>619; 6144</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>4279; 15396</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C06-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Habitat-trans_dic.xlsx
@@ -727,17 +727,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,44</t>
+          <t>0,0; 5,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,12</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,57</t>
+          <t>0,0; 3,19</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,06</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,77</t>
+          <t>0,0; 2,6</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,68</t>
+          <t>0,0; 2,91</t>
         </is>
       </c>
     </row>
@@ -862,17 +862,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,32</t>
+          <t>0,0; 2,1</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,86</t>
+          <t>0,0; 2,93</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,25</t>
+          <t>0,0; 4,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,76</t>
+          <t>0,0; 3,96</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,41</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,02</t>
+          <t>0,37; 3,0</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,49</t>
+          <t>0,0; 4,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,18</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,27</t>
+          <t>0,0; 5,33</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,1</t>
+          <t>0,0; 5,02</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 4,57</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,17 +1042,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,51</t>
+          <t>0,28; 3,57</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,31</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,94</t>
+          <t>0,0; 5,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,71; 6,56</t>
+          <t>0,79; 6,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,45</t>
+          <t>0,0; 4,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,88</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,4; 3,57</t>
+          <t>0,37; 3,27</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,21</t>
+          <t>0,37; 3,16</t>
         </is>
       </c>
     </row>
@@ -1282,32 +1282,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,07</t>
+          <t>0,32; 2,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,28</t>
+          <t>0,0; 1,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,68</t>
+          <t>0,71; 2,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,01; 1,67</t>
+          <t>0,17; 1,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,96</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1317,22 +1317,22 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,73</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,44</t>
+          <t>0,35; 1,43</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,84</t>
+          <t>0,08; 0,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 1,76</t>
+          <t>0,47; 1,73</t>
         </is>
       </c>
     </row>
@@ -1655,17 +1655,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3855</t>
+          <t>0; 3925</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 4267</t>
+          <t>0; 3915</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2931</t>
+          <t>0; 2624</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1685,7 +1685,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3247</t>
+          <t>0; 2963</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 4056</t>
+          <t>0; 3812</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4156</t>
+          <t>0; 4516</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2612</t>
+          <t>0; 2361</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3061</t>
+          <t>0; 3138</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>391; 4829</t>
+          <t>0; 4686</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1888,7 +1888,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 7969</t>
+          <t>0; 6620</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 3851</t>
+          <t>0; 2944</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3368</t>
+          <t>0; 3050</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1039; 8485</t>
+          <t>1049; 8422</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2066,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4093</t>
+          <t>0; 3688</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2327</t>
+          <t>0; 2220</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5003</t>
+          <t>0; 4252</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3917</t>
+          <t>0; 3858</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 4616</t>
+          <t>0; 5493</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>427; 5415</t>
+          <t>435; 5501</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4215</t>
+          <t>0; 3506</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 6578</t>
+          <t>0; 5258</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5522</t>
+          <t>0; 5503</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2284,17 +2284,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>723; 6641</t>
+          <t>799; 7041</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2829</t>
+          <t>0; 2831</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4288</t>
+          <t>0; 4106</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3698</t>
+          <t>0; 3504</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>749; 6752</t>
+          <t>702; 6194</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>784; 6820</t>
+          <t>787; 6728</t>
         </is>
       </c>
     </row>
@@ -2482,57 +2482,57 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1127; 7336</t>
+          <t>1128; 7279</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4644</t>
+          <t>0; 4974</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2657; 10494</t>
+          <t>2765; 11093</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 3836</t>
+          <t>0; 4001</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>18; 6120</t>
+          <t>622; 6206</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3520</t>
+          <t>0; 3513</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 8558</t>
+          <t>0; 8563</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5225</t>
+          <t>0; 4522</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2505; 10386</t>
+          <t>2520; 10312</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>619; 6144</t>
+          <t>612; 5975</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4279; 15396</t>
+          <t>4082; 15143</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C06-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IP19C06-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,54 +649,54 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>1,09%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0,33%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,53%</t>
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,52%</t>
         </is>
       </c>
     </row>
@@ -717,7 +717,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -727,17 +727,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -747,17 +747,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 7,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 1,68</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,6</t>
+          <t>0,0; 2,64</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,91</t>
+          <t>0,0; 2,59</t>
         </is>
       </c>
     </row>
@@ -794,44 +794,44 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,39%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,58%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
           <t>0,26%</t>
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>0,82%</t>
         </is>
       </c>
     </row>
@@ -862,37 +862,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
           <t>0,0; 2,93</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 4,12</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,96</t>
+          <t>0,29; 3,97</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,17 +902,17 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,3</t>
+          <t>0,0; 1,29</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,41</t>
+          <t>0,0; 1,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,0</t>
+          <t>0,23; 1,93</t>
         </is>
       </c>
     </row>
@@ -934,44 +934,44 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>1,08%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>1,51%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,39%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0,36%</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
           <t>1,29%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,62%</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,95</t>
+          <t>0,0; 5,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 4,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>0,0; 4,55</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,33</t>
+          <t>0,0; 4,96</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,02</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,57</t>
+          <t>0,0; 1,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,28; 3,57</t>
+          <t>0,28; 3,71</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,31</t>
+          <t>0,0; 2,5</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2,83%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,77%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2,79%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1,52%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>1,52%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,38%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 3,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,92</t>
+          <t>0,0; 4,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,79; 6,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,26</t>
+          <t>0,0; 5,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,77; 6,63</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,88</t>
+          <t>0,0; 2,15</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,27</t>
+          <t>0,37; 3,7</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 3,16</t>
+          <t>0,37; 3,34</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,61%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,35%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>0,91%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,38%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>1,47%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>0,61%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,85%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 1,2</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,32; 2,06</t>
+          <t>0,17; 1,78</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 0,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 2,83</t>
+          <t>0,0; 1,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,11</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,7</t>
+          <t>0,32; 2,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,95</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>0,7; 2,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,63</t>
+          <t>0,0; 0,62</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,43</t>
+          <t>0,34; 1,38</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,82</t>
+          <t>0,0; 0,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 1,73</t>
+          <t>0,42; 1,46</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1519,32 +1519,32 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>525</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1587,39 +1587,39 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>771</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>745</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>803</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>525</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>803</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2659</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1655,17 +1655,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 3925</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3915</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 2624</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1675,17 +1675,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4965</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4521</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2963</t>
+          <t>0; 2645</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 3812</t>
+          <t>0; 3866</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 4516</t>
+          <t>0; 4039</t>
         </is>
       </c>
     </row>
@@ -1722,37 +1722,37 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1790,37 +1790,37 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>641</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
           <t>582</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>617</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1730</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1332</t>
+          <t>1661</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>2301</t>
         </is>
       </c>
     </row>
@@ -1858,17 +1858,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 2361</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 3138</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 4686</t>
+          <t>0; 3239</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1878,17 +1878,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3295</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3672</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0; 6620</t>
+          <t>343; 4639</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1898,17 +1898,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 2944</t>
+          <t>0; 2924</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 3050</t>
+          <t>0; 3423</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1049; 8422</t>
+          <t>640; 5399</t>
         </is>
       </c>
     </row>
@@ -1930,32 +1930,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1998,57 +1998,57 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>1128</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>422</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>857</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>366</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>1986</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>700</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>1045</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>1986</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1467</t>
+          <t>1331</t>
         </is>
       </c>
     </row>
@@ -2066,17 +2066,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3688</t>
+          <t>0; 4609</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3587</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2220</t>
+          <t>0; 5104</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2086,17 +2086,17 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 4252</t>
+          <t>0; 3697</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3858</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5493</t>
+          <t>0; 1780</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2106,17 +2106,17 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>435; 5501</t>
+          <t>431; 5719</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 3506</t>
+          <t>0; 3508</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 5258</t>
+          <t>0; 5360</t>
         </is>
       </c>
     </row>
@@ -2133,7 +2133,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -2148,27 +2148,27 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,49 +2201,49 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>695</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>1365</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
           <t>1519</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2861</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>2859</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>695</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1365</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
           <t>2885</t>
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2862</t>
+          <t>2859</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2834</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 5503</t>
+          <t>0; 4602</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2284,17 +2284,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>799; 7041</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 2831</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4106</t>
+          <t>0; 5245</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2304,17 +2304,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>785; 6805</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 3504</t>
+          <t>0; 4008</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>702; 6194</t>
+          <t>706; 7011</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>787; 6728</t>
+          <t>770; 6945</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,49 +2409,49 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>2223</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1605</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
           <t>3230</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>1388</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>5758</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>1219</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2223</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2377</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>1219</t>
-        </is>
-      </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
           <t>5452</t>
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>7294</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4350</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1128; 7279</t>
+          <t>616; 6517</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 4974</t>
+          <t>0; 3503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2765; 11093</t>
+          <t>0; 5834</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4001</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>622; 6206</t>
+          <t>1142; 7087</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 3513</t>
+          <t>0; 5418</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 8563</t>
+          <t>2789; 10451</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4522</t>
+          <t>0; 4387</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2520; 10312</t>
+          <t>2413; 9915</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>612; 5975</t>
+          <t>0; 5556</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4082; 15143</t>
+          <t>3587; 12528</t>
         </is>
       </c>
     </row>
